--- a/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/14_metrics_outcomes.xlsx
+++ b/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/14_metrics_outcomes.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rb36653691f37424e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="Rc7ed30d3c8f94bc5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R34f86c5e37734358"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R4ad6dbefca514de6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="Rfb70f460c6d84ae1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R88fd10ccf3174f7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R78690a59563f4b40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R1dffb01366f74ea8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R7c0d3257fd77496a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R1b2397027dad4c73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="Rb1ae61b88f8541a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R17c9e06f77e9494f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -628,7 +628,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R884195254cec4ca3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09d1305aeff74446"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -809,7 +809,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O6" s="78" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Validate Executive Office cycle time (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for metrics outcomes.</x:v>
       </x:c>
       <x:c r="P6" s="41" t="str">
         <x:v>Medium</x:v>
@@ -859,7 +859,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O7" s="79" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Confirm Executive Office quality and exception rate (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this metrics outcomes record is used downstream.</x:v>
       </x:c>
       <x:c r="P7" s="45" t="str">
         <x:v>Medium</x:v>
@@ -909,7 +909,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O8" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Attach client evidence for Provider Operations cycle time (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P8" t="str">
         <x:v>Medium</x:v>
@@ -959,7 +959,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O9" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Reconcile Provider Operations quality and exception rate (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P9" t="str">
         <x:v>Medium</x:v>
@@ -1009,7 +1009,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O10" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Claims Operations cycle time (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P10" t="str">
         <x:v>Medium</x:v>
@@ -1059,7 +1059,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O11" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Validate Claims Operations quality and exception rate (record 6) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for metrics outcomes.</x:v>
       </x:c>
       <x:c r="P11" t="str">
         <x:v>Medium</x:v>
@@ -1109,7 +1109,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O12" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Confirm Eligibility and Benefits cycle time (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this metrics outcomes record is used downstream.</x:v>
       </x:c>
       <x:c r="P12" t="str">
         <x:v>Medium</x:v>
@@ -1159,7 +1159,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O13" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Attach client evidence for Eligibility and Benefits quality and exception rate (record 8), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P13" t="str">
         <x:v>Medium</x:v>
@@ -1209,7 +1209,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O14" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Reconcile Prior Authorization and UM cycle time (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P14" t="str">
         <x:v>Medium</x:v>
@@ -1259,7 +1259,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O15" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Prior Authorization and UM quality and exception rate (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P15" t="str">
         <x:v>Medium</x:v>
@@ -1282,7 +1282,7 @@
         <x:v>Member experience / contact center modernization and readiness program</x:v>
       </x:c>
       <x:c r="F16" t="str">
-        <x:v>Elapsed time or throughput measure for member calls, CRM case management, next-best-action workflows.</x:v>
+        <x:v>First contact resolution for claims-status calls for Agent Assist / Member Service; must be measured from cited source data, not inferred.</x:v>
       </x:c>
       <x:c r="G16" t="str">
         <x:v>7 days / 1750 monthly events synthetic</x:v>
@@ -1297,7 +1297,7 @@
         <x:v>Future-state roadmap TBD</x:v>
       </x:c>
       <x:c r="K16" t="str">
-        <x:v>Contact Center Member Service Operational Dataset</x:v>
+        <x:v>Genesys call sample with queue, intent, handle time, transfer flag, and after-call-work fields.</x:v>
       </x:c>
       <x:c r="L16" t="str">
         <x:v>Synthetic baseline for template depth proof; not realized value.</x:v>
@@ -1306,10 +1306,10 @@
         <x:v>Chief Experience Officer</x:v>
       </x:c>
       <x:c r="N16" t="str">
-        <x:v>Candidate baseline only</x:v>
+        <x:v>Candidate baseline; needs source-owner validation</x:v>
       </x:c>
       <x:c r="O16" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Validate Contact Center and Member Service cycle time (record 11) against Agent Assist / Member Service evidence: CRM-to-claims join gaps; confirm Genesys-Salesforce-claims context join owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P16" t="str">
         <x:v>Medium</x:v>
@@ -1332,7 +1332,7 @@
         <x:v>Member experience / contact center modernization and readiness program</x:v>
       </x:c>
       <x:c r="F17" t="str">
-        <x:v>Exception, defect, rework, denial, or issue rate for Contact Center and Member Service.</x:v>
+        <x:v>After-call work minutes per agent shift for Agent Assist / Member Service; must be measured from cited source data, not inferred.</x:v>
       </x:c>
       <x:c r="G17" t="str">
         <x:v>8% synthetic exception rate</x:v>
@@ -1347,7 +1347,7 @@
         <x:v>Future-state roadmap TBD</x:v>
       </x:c>
       <x:c r="K17" t="str">
-        <x:v>Contact Center Member Service Analytics Mart</x:v>
+        <x:v>Salesforce Health Cloud case extract with member inquiry categories and resolution dispositions.</x:v>
       </x:c>
       <x:c r="L17" t="str">
         <x:v>Planning-grade synthetic metric; requires source evidence.</x:v>
@@ -1356,10 +1356,10 @@
         <x:v>Chief Experience Officer</x:v>
       </x:c>
       <x:c r="N17" t="str">
-        <x:v>Needs validation</x:v>
+        <x:v>Candidate baseline; needs source-owner validation</x:v>
       </x:c>
       <x:c r="O17" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Validate Contact Center and Member Service quality and exception rate (record 12) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P17" t="str">
         <x:v>Medium</x:v>
@@ -1409,7 +1409,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O18" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Attach client evidence for Revenue Cycle Operations cycle time (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P18" t="str">
         <x:v>Medium</x:v>
@@ -1459,7 +1459,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O19" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Reconcile Revenue Cycle Operations quality and exception rate (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P19" t="str">
         <x:v>Medium</x:v>
@@ -1482,7 +1482,7 @@
         <x:v>Finance analytics modernization and readiness program</x:v>
       </x:c>
       <x:c r="F20" t="str">
-        <x:v>Elapsed time or throughput measure for GL/AP/AR/budget/vendor spend reporting, close analytics, FP&amp;A dashboards.</x:v>
+        <x:v>Manual reconciliation hours per close cycle for Finance Analytics; must be measured from cited source data, not inferred.</x:v>
       </x:c>
       <x:c r="G20" t="str">
         <x:v>9 days / 2050 monthly events synthetic</x:v>
@@ -1497,7 +1497,7 @@
         <x:v>Future-state roadmap TBD</x:v>
       </x:c>
       <x:c r="K20" t="str">
-        <x:v>Finance Mart GL AP AR Subject Area</x:v>
+        <x:v>Finance Gold Data Product design notes for Databricks target certification.</x:v>
       </x:c>
       <x:c r="L20" t="str">
         <x:v>Synthetic baseline for template depth proof; not realized value.</x:v>
@@ -1506,10 +1506,10 @@
         <x:v>CFO</x:v>
       </x:c>
       <x:c r="N20" t="str">
-        <x:v>Candidate baseline only</x:v>
+        <x:v>Candidate baseline; needs source-owner validation</x:v>
       </x:c>
       <x:c r="O20" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Validate Finance Analytics cycle time (record 15) against Finance Analytics evidence: incomplete lineage from ERP to BI; confirm cost-center hierarchy stewardship owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P20" t="str">
         <x:v>Medium</x:v>
@@ -1532,7 +1532,7 @@
         <x:v>Finance analytics modernization and readiness program</x:v>
       </x:c>
       <x:c r="F21" t="str">
-        <x:v>Exception, defect, rework, denial, or issue rate for Finance Analytics.</x:v>
+        <x:v>Close report refresh completion by 6:00 AM CT for Finance Analytics; must be measured from cited source data, not inferred.</x:v>
       </x:c>
       <x:c r="G21" t="str">
         <x:v>3% synthetic exception rate</x:v>
@@ -1547,7 +1547,7 @@
         <x:v>Future-state roadmap TBD</x:v>
       </x:c>
       <x:c r="K21" t="str">
-        <x:v>Vendor Spend and Contract Analytics Dataset</x:v>
+        <x:v>Oracle ERP Finance GL/AP/AR extract as of 2026-06 synthetic close cycle.</x:v>
       </x:c>
       <x:c r="L21" t="str">
         <x:v>Planning-grade synthetic metric; requires source evidence.</x:v>
@@ -1556,10 +1556,10 @@
         <x:v>CFO</x:v>
       </x:c>
       <x:c r="N21" t="str">
-        <x:v>Needs validation</x:v>
+        <x:v>Candidate baseline; needs source-owner validation</x:v>
       </x:c>
       <x:c r="O21" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Validate Finance Analytics quality and exception rate (record 16) against Finance Analytics evidence: inconsistent vendor spend definitions; confirm Databricks Finance Gold certification owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P21" t="str">
         <x:v>Medium</x:v>
@@ -1609,7 +1609,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O22" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Confirm Workforce Analytics cycle time (record 17) current-vs-target status, module boundary, volume baseline, and relationship links before this metrics outcomes record is used downstream.</x:v>
       </x:c>
       <x:c r="P22" t="str">
         <x:v>Medium</x:v>
@@ -1659,7 +1659,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O23" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Attach client evidence for Workforce Analytics quality and exception rate (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P23" t="str">
         <x:v>Medium</x:v>
@@ -1709,7 +1709,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O24" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Reconcile Clinical Quality Analytics cycle time (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P24" t="str">
         <x:v>Medium</x:v>
@@ -1759,7 +1759,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O25" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Clinical Quality Analytics quality and exception rate (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P25" t="str">
         <x:v>Medium</x:v>
@@ -1809,7 +1809,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O26" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Validate Claims and Payment Analytics cycle time (record 21) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for metrics outcomes.</x:v>
       </x:c>
       <x:c r="P26" t="str">
         <x:v>Medium</x:v>
@@ -1859,7 +1859,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O27" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Confirm Claims and Payment Analytics quality and exception rate (record 22) current-vs-target status, module boundary, volume baseline, and relationship links before this metrics outcomes record is used downstream.</x:v>
       </x:c>
       <x:c r="P27" t="str">
         <x:v>Medium</x:v>
@@ -1909,7 +1909,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O28" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Attach client evidence for Provider Performance Analytics cycle time (record 23), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P28" t="str">
         <x:v>Medium</x:v>
@@ -1959,7 +1959,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O29" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Reconcile Provider Performance Analytics quality and exception rate (record 24) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P29" t="str">
         <x:v>Medium</x:v>
@@ -2009,7 +2009,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O30" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Enterprise Data Platform cycle time (record 25) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P30" t="str">
         <x:v>Medium</x:v>
@@ -2059,7 +2059,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O31" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Validate Enterprise Data Platform quality and exception rate (record 26) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for metrics outcomes.</x:v>
       </x:c>
       <x:c r="P31" t="str">
         <x:v>Medium</x:v>
@@ -2109,7 +2109,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O32" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Confirm Data Governance and Data Quality cycle time (record 27) current-vs-target status, module boundary, volume baseline, and relationship links before this metrics outcomes record is used downstream.</x:v>
       </x:c>
       <x:c r="P32" t="str">
         <x:v>Medium</x:v>
@@ -2159,7 +2159,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O33" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Attach client evidence for Data Governance and Data Quality quality and exception rate (record 28), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P33" t="str">
         <x:v>Medium</x:v>
@@ -2182,7 +2182,7 @@
         <x:v>Agent Assist for member service modernization and readiness program</x:v>
       </x:c>
       <x:c r="F34" t="str">
-        <x:v>Elapsed time or throughput measure for agent assist, call summarization, intent detection, guided resolution.</x:v>
+        <x:v>First contact resolution for claims-status calls for Agent Assist / Member Service; must be measured from cited source data, not inferred.</x:v>
       </x:c>
       <x:c r="G34" t="str">
         <x:v>8 days / 3100 monthly events synthetic</x:v>
@@ -2197,7 +2197,7 @@
         <x:v>Future-state roadmap TBD</x:v>
       </x:c>
       <x:c r="K34" t="str">
-        <x:v>Agent Assist Next Best Action Operational Dataset</x:v>
+        <x:v>Knowledge article export with duplicate and stale article flags.</x:v>
       </x:c>
       <x:c r="L34" t="str">
         <x:v>Synthetic baseline for template depth proof; not realized value.</x:v>
@@ -2206,10 +2206,10 @@
         <x:v>VP Contact Center</x:v>
       </x:c>
       <x:c r="N34" t="str">
-        <x:v>Candidate baseline only</x:v>
+        <x:v>Candidate baseline; needs source-owner validation</x:v>
       </x:c>
       <x:c r="O34" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Validate Agent Assist and Next Best Action cycle time (record 29) against Agent Assist / Member Service evidence: CRM-to-claims join gaps; confirm Genesys-Salesforce-claims context join owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P34" t="str">
         <x:v>Medium</x:v>
@@ -2232,7 +2232,7 @@
         <x:v>Agent Assist for member service modernization and readiness program</x:v>
       </x:c>
       <x:c r="F35" t="str">
-        <x:v>Exception, defect, rework, denial, or issue rate for Agent Assist and Next Best Action.</x:v>
+        <x:v>After-call work minutes per agent shift for Agent Assist / Member Service; must be measured from cited source data, not inferred.</x:v>
       </x:c>
       <x:c r="G35" t="str">
         <x:v>3% synthetic exception rate</x:v>
@@ -2247,7 +2247,7 @@
         <x:v>Future-state roadmap TBD</x:v>
       </x:c>
       <x:c r="K35" t="str">
-        <x:v>Agent Assist Next Best Action Analytics Mart</x:v>
+        <x:v>Member service KPI baseline for AHT, FCR, transfer rate, complaint escalation, and quality score.</x:v>
       </x:c>
       <x:c r="L35" t="str">
         <x:v>Planning-grade synthetic metric; requires source evidence.</x:v>
@@ -2256,10 +2256,10 @@
         <x:v>VP Contact Center</x:v>
       </x:c>
       <x:c r="N35" t="str">
-        <x:v>Needs validation</x:v>
+        <x:v>Candidate baseline; needs source-owner validation</x:v>
       </x:c>
       <x:c r="O35" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Validate Agent Assist and Next Best Action quality and exception rate (record 30) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P35" t="str">
         <x:v>Medium</x:v>
@@ -2309,7 +2309,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O36" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Validate Unified Clinical and Claims Lakehouse cycle time (record 31) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for metrics outcomes.</x:v>
       </x:c>
       <x:c r="P36" t="str">
         <x:v>Medium</x:v>
@@ -2359,7 +2359,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O37" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Confirm Unified Clinical and Claims Lakehouse quality and exception rate (record 32) current-vs-target status, module boundary, volume baseline, and relationship links before this metrics outcomes record is used downstream.</x:v>
       </x:c>
       <x:c r="P37" t="str">
         <x:v>Medium</x:v>
@@ -2409,7 +2409,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O38" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Attach client evidence for IT Budget and Tower Baseline cycle time (record 33), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P38" t="str">
         <x:v>Medium</x:v>
@@ -2459,7 +2459,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O39" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Reconcile IT Budget and Tower Baseline quality and exception rate (record 34) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P39" t="str">
         <x:v>Medium</x:v>
@@ -2509,7 +2509,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O40" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Vendor and Contract Optimization cycle time (record 35) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P40" t="str">
         <x:v>Medium</x:v>
@@ -2559,7 +2559,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O41" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Validate Vendor and Contract Optimization quality and exception rate (record 36) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for metrics outcomes.</x:v>
       </x:c>
       <x:c r="P41" t="str">
         <x:v>Medium</x:v>
@@ -2609,7 +2609,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O42" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Confirm Infrastructure and CMDB cycle time (record 37) current-vs-target status, module boundary, volume baseline, and relationship links before this metrics outcomes record is used downstream.</x:v>
       </x:c>
       <x:c r="P42" t="str">
         <x:v>Medium</x:v>
@@ -2659,7 +2659,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O43" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Attach client evidence for Infrastructure and CMDB quality and exception rate (record 38), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P43" t="str">
         <x:v>Medium</x:v>
@@ -2709,7 +2709,7 @@
         <x:v>Candidate baseline only</x:v>
       </x:c>
       <x:c r="O44" t="str">
-        <x:v>Validate denominator, event taxonomy, source system and reporting cadence.</x:v>
+        <x:v>Reconcile Incident Problem Change Operations cycle time (record 39) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P44" t="str">
         <x:v>Medium</x:v>
@@ -2759,7 +2759,7 @@
         <x:v>Needs validation</x:v>
       </x:c>
       <x:c r="O45" t="str">
-        <x:v>Need exact business definition, owner approval, and traceable source.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Incident Problem Change Operations quality and exception rate (record 40) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P45" t="str">
         <x:v>Medium</x:v>
@@ -2783,7 +2783,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9886c2d22d2340d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f31808a44dd4727"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2858,7 +2858,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec43043b352046c2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99bad0062ce14b70"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3052,7 +3052,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d8ecd6477304bd2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98ec6f27fffb43c5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3122,7 +3122,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30b1b2a8266b4e57"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7de0b4fd1504800"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3232,7 +3232,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03a9bbc210164916"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R187cc005d71c4d0f"/>
   </x:tableParts>
 </x:worksheet>
 </file>